--- a/kahoot_sentences_22.xlsx
+++ b/kahoot_sentences_22.xlsx
@@ -133,7 +133,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who</t>
+          <t xml:space="preserve">His</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -658,14 +658,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t xml:space="preserve">表姊</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t xml:space="preserve">姪女</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姊姊</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">阿姨（姑姑、舅媽也是）</t>
@@ -673,7 +673,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">奶奶</t>
+          <t xml:space="preserve">叔叔</t>
         </is>
       </c>
       <c r="G25">
@@ -728,22 +728,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t xml:space="preserve">爸爸</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爺爺（外公也是）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">叔叔</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">奶奶</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爺爺（外公也是）</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">哥哥</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">叔叔</t>
         </is>
       </c>
       <c r="G27">
@@ -768,12 +768,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">It</t>
+          <t xml:space="preserve">His</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who</t>
+          <t xml:space="preserve">Him</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">

--- a/kahoot_sentences_22.xlsx
+++ b/kahoot_sentences_22.xlsx
@@ -198,7 +198,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Is she a nurse?" 改成直述句，要怎麼寫？</t>
+          <t xml:space="preserve">「她 是 一位 護理師。」英文怎麼說？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -268,27 +268,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">直述句變問句，是哪兩個字交換位置？</t>
+          <t xml:space="preserve">「他 是 你的 叔叔 嗎？」英文怎麼說？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">he 和 a</t>
+          <t xml:space="preserve">He is your uncle?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">he 和 is</t>
+          <t xml:space="preserve">Is he your uncle?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">is 和 a</t>
+          <t xml:space="preserve">Is your uncle he?</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 和 doctor</t>
+          <t xml:space="preserve">Is he uncle your?</t>
         </is>
       </c>
       <c r="G14">
